--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -61692,24 +61692,47 @@
     </row>
     <row r="2667">
       <c r="A2667" s="1" t="n">
-        <v>46205.2916666667</v>
+        <v>46204.2916666667</v>
       </c>
       <c r="B2667" t="n">
-        <v>4809884</v>
+        <v>4245754</v>
       </c>
       <c r="C2667" t="n">
-        <v>64.0699996948242</v>
+        <v>65.5699996948242</v>
       </c>
       <c r="D2667" t="n">
-        <v>61.0099983215332</v>
+        <v>61.8400001525879</v>
       </c>
       <c r="E2667" t="n">
-        <v>61.2000007629395</v>
+        <v>65</v>
       </c>
       <c r="F2667" t="n">
-        <v>61.8400001525879</v>
+        <v>62.3699989318848</v>
       </c>
       <c r="G2667" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2668">
+      <c r="A2668" s="1" t="n">
+        <v>46206.2916666667</v>
+      </c>
+      <c r="B2668" t="n">
+        <v>2029465</v>
+      </c>
+      <c r="C2668" t="n">
+        <v>62.9000015258789</v>
+      </c>
+      <c r="D2668" t="n">
+        <v>61.0200004577637</v>
+      </c>
+      <c r="E2668" t="n">
+        <v>61.0200004577637</v>
+      </c>
+      <c r="F2668" t="n">
+        <v>62.7700004577637</v>
+      </c>
+      <c r="G2668" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -62198,22 +62198,22 @@
     </row>
     <row r="2689">
       <c r="A2689" s="1" t="n">
-        <v>46237.2916666667</v>
+        <v>46234.2916666667</v>
       </c>
       <c r="B2689" t="n">
-        <v>5683363</v>
+        <v>6677927</v>
       </c>
       <c r="C2689" t="n">
-        <v>46.2799987792969</v>
+        <v>48.1800003051758</v>
       </c>
       <c r="D2689" t="n">
-        <v>44.0250015258789</v>
+        <v>45.4500007629395</v>
       </c>
       <c r="E2689" t="n">
-        <v>46.25</v>
+        <v>47.5</v>
       </c>
       <c r="F2689" t="n">
-        <v>45.2900009155273</v>
+        <v>45.6800003051758</v>
       </c>
       <c r="G2689" t="s">
         <v>7</v>
@@ -62221,22 +62221,22 @@
     </row>
     <row r="2690">
       <c r="A2690" s="1" t="n">
-        <v>46238.2916666667</v>
+        <v>46237.2916666667</v>
       </c>
       <c r="B2690" t="n">
-        <v>5413258</v>
+        <v>5683363</v>
       </c>
       <c r="C2690" t="n">
-        <v>47.6199989318848</v>
+        <v>46.2799987792969</v>
       </c>
       <c r="D2690" t="n">
-        <v>46.0699996948242</v>
+        <v>44.0250015258789</v>
       </c>
       <c r="E2690" t="n">
-        <v>46.2000007629395</v>
+        <v>46.25</v>
       </c>
       <c r="F2690" t="n">
-        <v>46.9199981689453</v>
+        <v>45.2900009155273</v>
       </c>
       <c r="G2690" t="s">
         <v>7</v>
@@ -62244,24 +62244,68 @@
     </row>
     <row r="2691">
       <c r="A2691" s="1" t="n">
+        <v>46238.2916666667</v>
+      </c>
+      <c r="B2691" t="n">
+        <v>5413258</v>
+      </c>
+      <c r="C2691" t="n">
+        <v>47.6199989318848</v>
+      </c>
+      <c r="D2691" t="n">
+        <v>46.0699996948242</v>
+      </c>
+      <c r="E2691" t="n">
+        <v>46.2000007629395</v>
+      </c>
+      <c r="F2691" t="n">
+        <v>46.9199981689453</v>
+      </c>
+      <c r="G2691" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2692">
+      <c r="A2692" s="1" t="n">
         <v>46239.2916666667</v>
       </c>
-      <c r="B2691" t="n">
+      <c r="B2692" t="n">
         <v>4462071</v>
       </c>
-      <c r="C2691" t="n">
+      <c r="C2692" t="n">
         <v>47.4000015258789</v>
       </c>
-      <c r="D2691" t="n">
+      <c r="D2692" t="n">
         <v>45.7449989318848</v>
       </c>
-      <c r="E2691" t="n">
+      <c r="E2692" t="n">
         <v>47.3499984741211</v>
       </c>
-      <c r="F2691" t="n">
+      <c r="F2692" t="n">
         <v>46.1749992370605</v>
       </c>
-      <c r="G2691" t="s">
+      <c r="G2692" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2693">
+      <c r="A2693" s="1" t="n">
+        <v>46240.2916666667</v>
+      </c>
+      <c r="B2693" t="n">
+        <v>4090576</v>
+      </c>
+      <c r="C2693" t="n">
+        <v>47.3400001525879</v>
+      </c>
+      <c r="D2693" t="n">
+        <v>45.2099990844727</v>
+      </c>
+      <c r="E2693" t="n">
+        <v>45.7050018310547</v>
+      </c>
+      <c r="F2693"/>
+      <c r="G2693" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -62334,6 +62334,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2695">
+      <c r="A2695" s="1" t="n">
+        <v>46245.2916666667</v>
+      </c>
+      <c r="B2695" t="n">
+        <v>2832118</v>
+      </c>
+      <c r="C2695" t="n">
+        <v>48.5750007629395</v>
+      </c>
+      <c r="D2695" t="n">
+        <v>47.2400016784668</v>
+      </c>
+      <c r="E2695" t="n">
+        <v>47.3650016784668</v>
+      </c>
+      <c r="F2695" t="n">
+        <v>47.7750015258789</v>
+      </c>
+      <c r="G2695" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -62357,6 +62357,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2696">
+      <c r="A2696" s="1" t="n">
+        <v>46246.2916666667</v>
+      </c>
+      <c r="B2696" t="n">
+        <v>4089878</v>
+      </c>
+      <c r="C2696" t="n">
+        <v>49.189998626709</v>
+      </c>
+      <c r="D2696" t="n">
+        <v>47.9749984741211</v>
+      </c>
+      <c r="E2696" t="n">
+        <v>48.3950004577637</v>
+      </c>
+      <c r="F2696" t="n">
+        <v>48.0499992370605</v>
+      </c>
+      <c r="G2696" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -61991,22 +61991,22 @@
     </row>
     <row r="2680">
       <c r="A2680" s="1" t="n">
-        <v>46223.2916666667</v>
+        <v>46224.2916666667</v>
       </c>
       <c r="B2680" t="n">
-        <v>2471279</v>
+        <v>3780143</v>
       </c>
       <c r="C2680" t="n">
-        <v>55.2999992370605</v>
+        <v>57.2999992370605</v>
       </c>
       <c r="D2680" t="n">
-        <v>53.8499984741211</v>
+        <v>55.8300018310547</v>
       </c>
       <c r="E2680" t="n">
-        <v>54.5099983215332</v>
+        <v>55.9599990844727</v>
       </c>
       <c r="F2680" t="n">
-        <v>54.8899993896484</v>
+        <v>57.2700004577637</v>
       </c>
       <c r="G2680" t="s">
         <v>7</v>
@@ -62014,22 +62014,22 @@
     </row>
     <row r="2681">
       <c r="A2681" s="1" t="n">
-        <v>46224.2916666667</v>
+        <v>46225.2916666667</v>
       </c>
       <c r="B2681" t="n">
-        <v>3780143</v>
+        <v>4522729</v>
       </c>
       <c r="C2681" t="n">
-        <v>57.2999992370605</v>
+        <v>58.2900009155273</v>
       </c>
       <c r="D2681" t="n">
-        <v>55.8300018310547</v>
+        <v>56.2799987792969</v>
       </c>
       <c r="E2681" t="n">
-        <v>55.9599990844727</v>
+        <v>56.7000007629395</v>
       </c>
       <c r="F2681" t="n">
-        <v>57.2700004577637</v>
+        <v>58.25</v>
       </c>
       <c r="G2681" t="s">
         <v>7</v>
@@ -62037,22 +62037,22 @@
     </row>
     <row r="2682">
       <c r="A2682" s="1" t="n">
-        <v>46225.2916666667</v>
+        <v>46226.2916666667</v>
       </c>
       <c r="B2682" t="n">
-        <v>4522729</v>
+        <v>19746787</v>
       </c>
       <c r="C2682" t="n">
-        <v>58.2900009155273</v>
+        <v>51.4799995422363</v>
       </c>
       <c r="D2682" t="n">
-        <v>56.2799987792969</v>
+        <v>47</v>
       </c>
       <c r="E2682" t="n">
-        <v>56.7000007629395</v>
+        <v>50.6800003051758</v>
       </c>
       <c r="F2682" t="n">
-        <v>58.25</v>
+        <v>47.939998626709</v>
       </c>
       <c r="G2682" t="s">
         <v>7</v>
@@ -62060,22 +62060,22 @@
     </row>
     <row r="2683">
       <c r="A2683" s="1" t="n">
-        <v>46226.2916666667</v>
+        <v>46227.2916666667</v>
       </c>
       <c r="B2683" t="n">
-        <v>19746787</v>
+        <v>6387250</v>
       </c>
       <c r="C2683" t="n">
-        <v>51.4799995422363</v>
+        <v>48.5900001525879</v>
       </c>
       <c r="D2683" t="n">
-        <v>47</v>
+        <v>46.1450004577637</v>
       </c>
       <c r="E2683" t="n">
-        <v>50.6800003051758</v>
+        <v>47.2400016784668</v>
       </c>
       <c r="F2683" t="n">
-        <v>47.939998626709</v>
+        <v>46.7849998474121</v>
       </c>
       <c r="G2683" t="s">
         <v>7</v>
@@ -62083,22 +62083,22 @@
     </row>
     <row r="2684">
       <c r="A2684" s="1" t="n">
-        <v>46227.2916666667</v>
+        <v>46230.2916666667</v>
       </c>
       <c r="B2684" t="n">
-        <v>6387250</v>
+        <v>7301606</v>
       </c>
       <c r="C2684" t="n">
-        <v>48.5900001525879</v>
+        <v>48.0099983215332</v>
       </c>
       <c r="D2684" t="n">
-        <v>46.1450004577637</v>
+        <v>45.4500007629395</v>
       </c>
       <c r="E2684" t="n">
-        <v>47.2400016784668</v>
+        <v>46.685001373291</v>
       </c>
       <c r="F2684" t="n">
-        <v>46.7849998474121</v>
+        <v>45.8950004577637</v>
       </c>
       <c r="G2684" t="s">
         <v>7</v>
@@ -62106,22 +62106,22 @@
     </row>
     <row r="2685">
       <c r="A2685" s="1" t="n">
-        <v>46230.2916666667</v>
+        <v>46231.2916666667</v>
       </c>
       <c r="B2685" t="n">
-        <v>7301606</v>
+        <v>9013687</v>
       </c>
       <c r="C2685" t="n">
-        <v>48.0099983215332</v>
+        <v>46.25</v>
       </c>
       <c r="D2685" t="n">
-        <v>45.4500007629395</v>
+        <v>43.060001373291</v>
       </c>
       <c r="E2685" t="n">
-        <v>46.685001373291</v>
+        <v>45.1749992370605</v>
       </c>
       <c r="F2685" t="n">
-        <v>45.8950004577637</v>
+        <v>44.4949989318848</v>
       </c>
       <c r="G2685" t="s">
         <v>7</v>
@@ -62129,22 +62129,22 @@
     </row>
     <row r="2686">
       <c r="A2686" s="1" t="n">
-        <v>46231.2916666667</v>
+        <v>46232.2916666667</v>
       </c>
       <c r="B2686" t="n">
-        <v>9013687</v>
+        <v>7583765</v>
       </c>
       <c r="C2686" t="n">
-        <v>46.25</v>
+        <v>44.6150016784668</v>
       </c>
       <c r="D2686" t="n">
-        <v>43.060001373291</v>
+        <v>42.4150009155273</v>
       </c>
       <c r="E2686" t="n">
-        <v>45.1749992370605</v>
+        <v>43.4249992370605</v>
       </c>
       <c r="F2686" t="n">
-        <v>44.4949989318848</v>
+        <v>42.9150009155273</v>
       </c>
       <c r="G2686" t="s">
         <v>7</v>
@@ -62152,22 +62152,22 @@
     </row>
     <row r="2687">
       <c r="A2687" s="1" t="n">
-        <v>46232.2916666667</v>
+        <v>46233.2916666667</v>
       </c>
       <c r="B2687" t="n">
-        <v>7583765</v>
+        <v>6370784</v>
       </c>
       <c r="C2687" t="n">
-        <v>44.6150016784668</v>
+        <v>45.9500007629395</v>
       </c>
       <c r="D2687" t="n">
-        <v>42.4150009155273</v>
+        <v>42.6800003051758</v>
       </c>
       <c r="E2687" t="n">
-        <v>43.4249992370605</v>
+        <v>42.7599983215332</v>
       </c>
       <c r="F2687" t="n">
-        <v>42.9150009155273</v>
+        <v>45.6399993896484</v>
       </c>
       <c r="G2687" t="s">
         <v>7</v>
@@ -62175,22 +62175,22 @@
     </row>
     <row r="2688">
       <c r="A2688" s="1" t="n">
-        <v>46233.2916666667</v>
+        <v>46237.2916666667</v>
       </c>
       <c r="B2688" t="n">
-        <v>6370784</v>
+        <v>5683363</v>
       </c>
       <c r="C2688" t="n">
-        <v>45.9500007629395</v>
+        <v>46.2799987792969</v>
       </c>
       <c r="D2688" t="n">
-        <v>42.6800003051758</v>
+        <v>44.0250015258789</v>
       </c>
       <c r="E2688" t="n">
-        <v>42.7599983215332</v>
+        <v>46.25</v>
       </c>
       <c r="F2688" t="n">
-        <v>45.6399993896484</v>
+        <v>45.2900009155273</v>
       </c>
       <c r="G2688" t="s">
         <v>7</v>
@@ -62198,22 +62198,22 @@
     </row>
     <row r="2689">
       <c r="A2689" s="1" t="n">
-        <v>46237.2916666667</v>
+        <v>46238.2916666667</v>
       </c>
       <c r="B2689" t="n">
-        <v>5683363</v>
+        <v>5413258</v>
       </c>
       <c r="C2689" t="n">
-        <v>46.2799987792969</v>
+        <v>47.6199989318848</v>
       </c>
       <c r="D2689" t="n">
-        <v>44.0250015258789</v>
+        <v>46.0699996948242</v>
       </c>
       <c r="E2689" t="n">
-        <v>46.25</v>
+        <v>46.2000007629395</v>
       </c>
       <c r="F2689" t="n">
-        <v>45.2900009155273</v>
+        <v>46.9199981689453</v>
       </c>
       <c r="G2689" t="s">
         <v>7</v>
@@ -62221,22 +62221,22 @@
     </row>
     <row r="2690">
       <c r="A2690" s="1" t="n">
-        <v>46238.2916666667</v>
+        <v>46239.2916666667</v>
       </c>
       <c r="B2690" t="n">
-        <v>5413258</v>
+        <v>4462071</v>
       </c>
       <c r="C2690" t="n">
-        <v>47.6199989318848</v>
+        <v>47.4000015258789</v>
       </c>
       <c r="D2690" t="n">
-        <v>46.0699996948242</v>
+        <v>45.7449989318848</v>
       </c>
       <c r="E2690" t="n">
-        <v>46.2000007629395</v>
+        <v>47.3499984741211</v>
       </c>
       <c r="F2690" t="n">
-        <v>46.9199981689453</v>
+        <v>46.1749992370605</v>
       </c>
       <c r="G2690" t="s">
         <v>7</v>
@@ -62244,22 +62244,22 @@
     </row>
     <row r="2691">
       <c r="A2691" s="1" t="n">
-        <v>46239.2916666667</v>
+        <v>46240.2916666667</v>
       </c>
       <c r="B2691" t="n">
-        <v>4462071</v>
+        <v>4090576</v>
       </c>
       <c r="C2691" t="n">
-        <v>47.4000015258789</v>
+        <v>47.3400001525879</v>
       </c>
       <c r="D2691" t="n">
-        <v>45.7449989318848</v>
+        <v>45.2099990844727</v>
       </c>
       <c r="E2691" t="n">
-        <v>47.3499984741211</v>
+        <v>45.7050018310547</v>
       </c>
       <c r="F2691" t="n">
-        <v>46.1749992370605</v>
+        <v>46.7649993896484</v>
       </c>
       <c r="G2691" t="s">
         <v>7</v>
@@ -62267,22 +62267,22 @@
     </row>
     <row r="2692">
       <c r="A2692" s="1" t="n">
-        <v>46240.2916666667</v>
+        <v>46241.2916666667</v>
       </c>
       <c r="B2692" t="n">
-        <v>4090576</v>
+        <v>4017448</v>
       </c>
       <c r="C2692" t="n">
-        <v>47.3400001525879</v>
+        <v>48.5200004577637</v>
       </c>
       <c r="D2692" t="n">
-        <v>45.2099990844727</v>
+        <v>46.5800018310547</v>
       </c>
       <c r="E2692" t="n">
-        <v>45.7050018310547</v>
+        <v>46.6199989318848</v>
       </c>
       <c r="F2692" t="n">
-        <v>46.7649993896484</v>
+        <v>48.2350006103516</v>
       </c>
       <c r="G2692" t="s">
         <v>7</v>
@@ -62290,22 +62290,22 @@
     </row>
     <row r="2693">
       <c r="A2693" s="1" t="n">
-        <v>46241.2916666667</v>
+        <v>46244.2916666667</v>
       </c>
       <c r="B2693" t="n">
-        <v>4017448</v>
+        <v>3940565</v>
       </c>
       <c r="C2693" t="n">
-        <v>48.5200004577637</v>
+        <v>49.5699996948242</v>
       </c>
       <c r="D2693" t="n">
-        <v>46.5800018310547</v>
+        <v>47.7750015258789</v>
       </c>
       <c r="E2693" t="n">
-        <v>46.6199989318848</v>
+        <v>48.5999984741211</v>
       </c>
       <c r="F2693" t="n">
-        <v>48.2350006103516</v>
+        <v>47.7750015258789</v>
       </c>
       <c r="G2693" t="s">
         <v>7</v>
@@ -62313,19 +62313,19 @@
     </row>
     <row r="2694">
       <c r="A2694" s="1" t="n">
-        <v>46244.2916666667</v>
+        <v>46245.2916666667</v>
       </c>
       <c r="B2694" t="n">
-        <v>3940565</v>
+        <v>2832118</v>
       </c>
       <c r="C2694" t="n">
-        <v>49.5699996948242</v>
+        <v>48.5750007629395</v>
       </c>
       <c r="D2694" t="n">
-        <v>47.7750015258789</v>
+        <v>47.2400016784668</v>
       </c>
       <c r="E2694" t="n">
-        <v>48.5999984741211</v>
+        <v>47.3650016784668</v>
       </c>
       <c r="F2694" t="n">
         <v>47.7750015258789</v>
@@ -62336,22 +62336,22 @@
     </row>
     <row r="2695">
       <c r="A2695" s="1" t="n">
-        <v>46245.2916666667</v>
+        <v>46246.2916666667</v>
       </c>
       <c r="B2695" t="n">
-        <v>2832118</v>
+        <v>4089878</v>
       </c>
       <c r="C2695" t="n">
-        <v>48.5750007629395</v>
+        <v>49.189998626709</v>
       </c>
       <c r="D2695" t="n">
-        <v>47.2400016784668</v>
+        <v>47.9749984741211</v>
       </c>
       <c r="E2695" t="n">
-        <v>47.3650016784668</v>
+        <v>48.3950004577637</v>
       </c>
       <c r="F2695" t="n">
-        <v>47.7750015258789</v>
+        <v>48.0499992370605</v>
       </c>
       <c r="G2695" t="s">
         <v>7</v>
@@ -62359,22 +62359,22 @@
     </row>
     <row r="2696">
       <c r="A2696" s="1" t="n">
-        <v>46246.2916666667</v>
+        <v>46247.2916666667</v>
       </c>
       <c r="B2696" t="n">
-        <v>4089878</v>
+        <v>3743345</v>
       </c>
       <c r="C2696" t="n">
-        <v>49.189998626709</v>
+        <v>48</v>
       </c>
       <c r="D2696" t="n">
-        <v>47.9749984741211</v>
+        <v>46.9500007629395</v>
       </c>
       <c r="E2696" t="n">
-        <v>48.3950004577637</v>
+        <v>48</v>
       </c>
       <c r="F2696" t="n">
-        <v>48.0499992370605</v>
+        <v>47.6150016784668</v>
       </c>
       <c r="G2696" t="s">
         <v>7</v>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -62380,6 +62380,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2697">
+      <c r="A2697" s="1" t="n">
+        <v>46248.2916666667</v>
+      </c>
+      <c r="B2697" t="n">
+        <v>3059941</v>
+      </c>
+      <c r="C2697" t="n">
+        <v>47.5900001525879</v>
+      </c>
+      <c r="D2697" t="n">
+        <v>46.625</v>
+      </c>
+      <c r="E2697" t="n">
+        <v>47.0849990844727</v>
+      </c>
+      <c r="F2697" t="n">
+        <v>46.689998626709</v>
+      </c>
+      <c r="G2697" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -62449,6 +62449,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2700">
+      <c r="A2700" s="1" t="n">
+        <v>46253.2916666667</v>
+      </c>
+      <c r="B2700" t="n">
+        <v>6165794</v>
+      </c>
+      <c r="C2700" t="n">
+        <v>45.6100006103516</v>
+      </c>
+      <c r="D2700" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="E2700" t="n">
+        <v>45.4099998474121</v>
+      </c>
+      <c r="F2700" t="n">
+        <v>43.9599990844727</v>
+      </c>
+      <c r="G2700" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -61991,22 +61991,22 @@
     </row>
     <row r="2680">
       <c r="A2680" s="1" t="n">
-        <v>46224.2916666667</v>
+        <v>46223.2916666667</v>
       </c>
       <c r="B2680" t="n">
-        <v>3780143</v>
+        <v>2471279</v>
       </c>
       <c r="C2680" t="n">
-        <v>57.2999992370605</v>
+        <v>55.2999992370605</v>
       </c>
       <c r="D2680" t="n">
-        <v>55.8300018310547</v>
+        <v>53.8499984741211</v>
       </c>
       <c r="E2680" t="n">
-        <v>55.9599990844727</v>
+        <v>54.5099983215332</v>
       </c>
       <c r="F2680" t="n">
-        <v>57.2700004577637</v>
+        <v>54.8899993896484</v>
       </c>
       <c r="G2680" t="s">
         <v>7</v>
@@ -62014,22 +62014,22 @@
     </row>
     <row r="2681">
       <c r="A2681" s="1" t="n">
-        <v>46225.2916666667</v>
+        <v>46224.2916666667</v>
       </c>
       <c r="B2681" t="n">
-        <v>4522729</v>
+        <v>3780143</v>
       </c>
       <c r="C2681" t="n">
-        <v>58.2900009155273</v>
+        <v>57.2999992370605</v>
       </c>
       <c r="D2681" t="n">
-        <v>56.2799987792969</v>
+        <v>55.8300018310547</v>
       </c>
       <c r="E2681" t="n">
-        <v>56.7000007629395</v>
+        <v>55.9599990844727</v>
       </c>
       <c r="F2681" t="n">
-        <v>58.25</v>
+        <v>57.2700004577637</v>
       </c>
       <c r="G2681" t="s">
         <v>7</v>
@@ -62037,22 +62037,22 @@
     </row>
     <row r="2682">
       <c r="A2682" s="1" t="n">
-        <v>46226.2916666667</v>
+        <v>46225.2916666667</v>
       </c>
       <c r="B2682" t="n">
-        <v>19746787</v>
+        <v>4522729</v>
       </c>
       <c r="C2682" t="n">
-        <v>51.4799995422363</v>
+        <v>58.2900009155273</v>
       </c>
       <c r="D2682" t="n">
-        <v>47</v>
+        <v>56.2799987792969</v>
       </c>
       <c r="E2682" t="n">
-        <v>50.6800003051758</v>
+        <v>56.7000007629395</v>
       </c>
       <c r="F2682" t="n">
-        <v>47.939998626709</v>
+        <v>58.25</v>
       </c>
       <c r="G2682" t="s">
         <v>7</v>
@@ -62060,22 +62060,22 @@
     </row>
     <row r="2683">
       <c r="A2683" s="1" t="n">
-        <v>46227.2916666667</v>
+        <v>46226.2916666667</v>
       </c>
       <c r="B2683" t="n">
-        <v>6387250</v>
+        <v>19746787</v>
       </c>
       <c r="C2683" t="n">
-        <v>48.5900001525879</v>
+        <v>51.4799995422363</v>
       </c>
       <c r="D2683" t="n">
-        <v>46.1450004577637</v>
+        <v>47</v>
       </c>
       <c r="E2683" t="n">
-        <v>47.2400016784668</v>
+        <v>50.6800003051758</v>
       </c>
       <c r="F2683" t="n">
-        <v>46.7849998474121</v>
+        <v>47.939998626709</v>
       </c>
       <c r="G2683" t="s">
         <v>7</v>
@@ -62083,22 +62083,22 @@
     </row>
     <row r="2684">
       <c r="A2684" s="1" t="n">
-        <v>46230.2916666667</v>
+        <v>46227.2916666667</v>
       </c>
       <c r="B2684" t="n">
-        <v>7301606</v>
+        <v>6387250</v>
       </c>
       <c r="C2684" t="n">
-        <v>48.0099983215332</v>
+        <v>48.5900001525879</v>
       </c>
       <c r="D2684" t="n">
-        <v>45.4500007629395</v>
+        <v>46.1450004577637</v>
       </c>
       <c r="E2684" t="n">
-        <v>46.685001373291</v>
+        <v>47.2400016784668</v>
       </c>
       <c r="F2684" t="n">
-        <v>45.8950004577637</v>
+        <v>46.7849998474121</v>
       </c>
       <c r="G2684" t="s">
         <v>7</v>
@@ -62106,22 +62106,22 @@
     </row>
     <row r="2685">
       <c r="A2685" s="1" t="n">
-        <v>46231.2916666667</v>
+        <v>46230.2916666667</v>
       </c>
       <c r="B2685" t="n">
-        <v>9013687</v>
+        <v>7301606</v>
       </c>
       <c r="C2685" t="n">
-        <v>46.25</v>
+        <v>48.0099983215332</v>
       </c>
       <c r="D2685" t="n">
-        <v>43.060001373291</v>
+        <v>45.4500007629395</v>
       </c>
       <c r="E2685" t="n">
-        <v>45.1749992370605</v>
+        <v>46.685001373291</v>
       </c>
       <c r="F2685" t="n">
-        <v>44.4949989318848</v>
+        <v>45.8950004577637</v>
       </c>
       <c r="G2685" t="s">
         <v>7</v>
@@ -62129,22 +62129,22 @@
     </row>
     <row r="2686">
       <c r="A2686" s="1" t="n">
-        <v>46232.2916666667</v>
+        <v>46231.2916666667</v>
       </c>
       <c r="B2686" t="n">
-        <v>7583765</v>
+        <v>9013687</v>
       </c>
       <c r="C2686" t="n">
-        <v>44.6150016784668</v>
+        <v>46.25</v>
       </c>
       <c r="D2686" t="n">
-        <v>42.4150009155273</v>
+        <v>43.060001373291</v>
       </c>
       <c r="E2686" t="n">
-        <v>43.4249992370605</v>
+        <v>45.1749992370605</v>
       </c>
       <c r="F2686" t="n">
-        <v>42.9150009155273</v>
+        <v>44.4949989318848</v>
       </c>
       <c r="G2686" t="s">
         <v>7</v>
@@ -62152,22 +62152,22 @@
     </row>
     <row r="2687">
       <c r="A2687" s="1" t="n">
-        <v>46233.2916666667</v>
+        <v>46232.2916666667</v>
       </c>
       <c r="B2687" t="n">
-        <v>6370784</v>
+        <v>7583765</v>
       </c>
       <c r="C2687" t="n">
-        <v>45.9500007629395</v>
+        <v>44.6150016784668</v>
       </c>
       <c r="D2687" t="n">
-        <v>42.6800003051758</v>
+        <v>42.4150009155273</v>
       </c>
       <c r="E2687" t="n">
-        <v>42.7599983215332</v>
+        <v>43.4249992370605</v>
       </c>
       <c r="F2687" t="n">
-        <v>45.6399993896484</v>
+        <v>42.9150009155273</v>
       </c>
       <c r="G2687" t="s">
         <v>7</v>
@@ -62175,22 +62175,22 @@
     </row>
     <row r="2688">
       <c r="A2688" s="1" t="n">
-        <v>46237.2916666667</v>
+        <v>46233.2916666667</v>
       </c>
       <c r="B2688" t="n">
-        <v>5683363</v>
+        <v>6370784</v>
       </c>
       <c r="C2688" t="n">
-        <v>46.2799987792969</v>
+        <v>45.9500007629395</v>
       </c>
       <c r="D2688" t="n">
-        <v>44.0250015258789</v>
+        <v>42.6800003051758</v>
       </c>
       <c r="E2688" t="n">
-        <v>46.25</v>
+        <v>42.7599983215332</v>
       </c>
       <c r="F2688" t="n">
-        <v>45.2900009155273</v>
+        <v>45.6399993896484</v>
       </c>
       <c r="G2688" t="s">
         <v>7</v>
@@ -62198,22 +62198,22 @@
     </row>
     <row r="2689">
       <c r="A2689" s="1" t="n">
-        <v>46238.2916666667</v>
+        <v>46237.2916666667</v>
       </c>
       <c r="B2689" t="n">
-        <v>5413258</v>
+        <v>5683363</v>
       </c>
       <c r="C2689" t="n">
-        <v>47.6199989318848</v>
+        <v>46.2799987792969</v>
       </c>
       <c r="D2689" t="n">
-        <v>46.0699996948242</v>
+        <v>44.0250015258789</v>
       </c>
       <c r="E2689" t="n">
-        <v>46.2000007629395</v>
+        <v>46.25</v>
       </c>
       <c r="F2689" t="n">
-        <v>46.9199981689453</v>
+        <v>45.2900009155273</v>
       </c>
       <c r="G2689" t="s">
         <v>7</v>
@@ -62221,22 +62221,22 @@
     </row>
     <row r="2690">
       <c r="A2690" s="1" t="n">
-        <v>46239.2916666667</v>
+        <v>46238.2916666667</v>
       </c>
       <c r="B2690" t="n">
-        <v>4462071</v>
+        <v>5413258</v>
       </c>
       <c r="C2690" t="n">
-        <v>47.4000015258789</v>
+        <v>47.6199989318848</v>
       </c>
       <c r="D2690" t="n">
-        <v>45.7449989318848</v>
+        <v>46.0699996948242</v>
       </c>
       <c r="E2690" t="n">
-        <v>47.3499984741211</v>
+        <v>46.2000007629395</v>
       </c>
       <c r="F2690" t="n">
-        <v>46.1749992370605</v>
+        <v>46.9199981689453</v>
       </c>
       <c r="G2690" t="s">
         <v>7</v>
@@ -62244,22 +62244,22 @@
     </row>
     <row r="2691">
       <c r="A2691" s="1" t="n">
-        <v>46240.2916666667</v>
+        <v>46239.2916666667</v>
       </c>
       <c r="B2691" t="n">
-        <v>4090576</v>
+        <v>4462071</v>
       </c>
       <c r="C2691" t="n">
-        <v>47.3400001525879</v>
+        <v>47.4000015258789</v>
       </c>
       <c r="D2691" t="n">
-        <v>45.2099990844727</v>
+        <v>45.7449989318848</v>
       </c>
       <c r="E2691" t="n">
-        <v>45.7050018310547</v>
+        <v>47.3499984741211</v>
       </c>
       <c r="F2691" t="n">
-        <v>46.7649993896484</v>
+        <v>46.1749992370605</v>
       </c>
       <c r="G2691" t="s">
         <v>7</v>
@@ -62267,22 +62267,22 @@
     </row>
     <row r="2692">
       <c r="A2692" s="1" t="n">
-        <v>46241.2916666667</v>
+        <v>46240.2916666667</v>
       </c>
       <c r="B2692" t="n">
-        <v>4017448</v>
+        <v>4090576</v>
       </c>
       <c r="C2692" t="n">
-        <v>48.5200004577637</v>
+        <v>47.3400001525879</v>
       </c>
       <c r="D2692" t="n">
-        <v>46.5800018310547</v>
+        <v>45.2099990844727</v>
       </c>
       <c r="E2692" t="n">
-        <v>46.6199989318848</v>
+        <v>45.7050018310547</v>
       </c>
       <c r="F2692" t="n">
-        <v>48.2350006103516</v>
+        <v>46.7649993896484</v>
       </c>
       <c r="G2692" t="s">
         <v>7</v>
@@ -62290,22 +62290,22 @@
     </row>
     <row r="2693">
       <c r="A2693" s="1" t="n">
-        <v>46244.2916666667</v>
+        <v>46241.2916666667</v>
       </c>
       <c r="B2693" t="n">
-        <v>3940565</v>
+        <v>4017448</v>
       </c>
       <c r="C2693" t="n">
-        <v>49.5699996948242</v>
+        <v>48.5200004577637</v>
       </c>
       <c r="D2693" t="n">
-        <v>47.7750015258789</v>
+        <v>46.5800018310547</v>
       </c>
       <c r="E2693" t="n">
-        <v>48.5999984741211</v>
+        <v>46.6199989318848</v>
       </c>
       <c r="F2693" t="n">
-        <v>47.7750015258789</v>
+        <v>48.2350006103516</v>
       </c>
       <c r="G2693" t="s">
         <v>7</v>
@@ -62313,19 +62313,19 @@
     </row>
     <row r="2694">
       <c r="A2694" s="1" t="n">
-        <v>46245.2916666667</v>
+        <v>46244.2916666667</v>
       </c>
       <c r="B2694" t="n">
-        <v>2832118</v>
+        <v>3940565</v>
       </c>
       <c r="C2694" t="n">
-        <v>48.5750007629395</v>
+        <v>49.5699996948242</v>
       </c>
       <c r="D2694" t="n">
-        <v>47.2400016784668</v>
+        <v>47.7750015258789</v>
       </c>
       <c r="E2694" t="n">
-        <v>47.3650016784668</v>
+        <v>48.5999984741211</v>
       </c>
       <c r="F2694" t="n">
         <v>47.7750015258789</v>
@@ -62336,22 +62336,22 @@
     </row>
     <row r="2695">
       <c r="A2695" s="1" t="n">
-        <v>46246.2916666667</v>
+        <v>46245.2916666667</v>
       </c>
       <c r="B2695" t="n">
-        <v>4089878</v>
+        <v>2832118</v>
       </c>
       <c r="C2695" t="n">
-        <v>49.189998626709</v>
+        <v>48.5750007629395</v>
       </c>
       <c r="D2695" t="n">
-        <v>47.9749984741211</v>
+        <v>47.2400016784668</v>
       </c>
       <c r="E2695" t="n">
-        <v>48.3950004577637</v>
+        <v>47.3650016784668</v>
       </c>
       <c r="F2695" t="n">
-        <v>48.0499992370605</v>
+        <v>47.7750015258789</v>
       </c>
       <c r="G2695" t="s">
         <v>7</v>
@@ -62359,22 +62359,22 @@
     </row>
     <row r="2696">
       <c r="A2696" s="1" t="n">
-        <v>46247.2916666667</v>
+        <v>46246.2916666667</v>
       </c>
       <c r="B2696" t="n">
-        <v>3743345</v>
+        <v>4089878</v>
       </c>
       <c r="C2696" t="n">
-        <v>48</v>
+        <v>49.189998626709</v>
       </c>
       <c r="D2696" t="n">
-        <v>46.9500007629395</v>
+        <v>47.9749984741211</v>
       </c>
       <c r="E2696" t="n">
-        <v>48</v>
+        <v>48.3950004577637</v>
       </c>
       <c r="F2696" t="n">
-        <v>47.6150016784668</v>
+        <v>48.0499992370605</v>
       </c>
       <c r="G2696" t="s">
         <v>7</v>
@@ -62382,22 +62382,22 @@
     </row>
     <row r="2697">
       <c r="A2697" s="1" t="n">
-        <v>46248.2916666667</v>
+        <v>46247.2916666667</v>
       </c>
       <c r="B2697" t="n">
-        <v>3059941</v>
+        <v>3743345</v>
       </c>
       <c r="C2697" t="n">
-        <v>47.5900001525879</v>
+        <v>48</v>
       </c>
       <c r="D2697" t="n">
-        <v>46.625</v>
+        <v>46.9500007629395</v>
       </c>
       <c r="E2697" t="n">
-        <v>47.0849990844727</v>
+        <v>48</v>
       </c>
       <c r="F2697" t="n">
-        <v>46.689998626709</v>
+        <v>47.6150016784668</v>
       </c>
       <c r="G2697" t="s">
         <v>7</v>
@@ -62405,22 +62405,22 @@
     </row>
     <row r="2698">
       <c r="A2698" s="1" t="n">
-        <v>46251.2916666667</v>
+        <v>46248.2916666667</v>
       </c>
       <c r="B2698" t="n">
-        <v>4934253</v>
+        <v>3059941</v>
       </c>
       <c r="C2698" t="n">
-        <v>49.0950012207031</v>
+        <v>47.5900001525879</v>
       </c>
       <c r="D2698" t="n">
-        <v>47.8950004577637</v>
+        <v>46.625</v>
       </c>
       <c r="E2698" t="n">
-        <v>48.2150001525879</v>
+        <v>47.0849990844727</v>
       </c>
       <c r="F2698" t="n">
-        <v>49.0400009155273</v>
+        <v>46.689998626709</v>
       </c>
       <c r="G2698" t="s">
         <v>7</v>
@@ -62428,22 +62428,22 @@
     </row>
     <row r="2699">
       <c r="A2699" s="1" t="n">
-        <v>46252.2916666667</v>
+        <v>46251.2916666667</v>
       </c>
       <c r="B2699" t="n">
-        <v>7065526</v>
+        <v>4934253</v>
       </c>
       <c r="C2699" t="n">
-        <v>47.935001373291</v>
+        <v>49.0950012207031</v>
       </c>
       <c r="D2699" t="n">
-        <v>45.185001373291</v>
+        <v>47.8950004577637</v>
       </c>
       <c r="E2699" t="n">
-        <v>47.9000015258789</v>
+        <v>48.2150001525879</v>
       </c>
       <c r="F2699" t="n">
-        <v>45.3300018310547</v>
+        <v>49.0400009155273</v>
       </c>
       <c r="G2699" t="s">
         <v>7</v>
@@ -62451,24 +62451,70 @@
     </row>
     <row r="2700">
       <c r="A2700" s="1" t="n">
+        <v>46252.2916666667</v>
+      </c>
+      <c r="B2700" t="n">
+        <v>7065526</v>
+      </c>
+      <c r="C2700" t="n">
+        <v>47.935001373291</v>
+      </c>
+      <c r="D2700" t="n">
+        <v>45.185001373291</v>
+      </c>
+      <c r="E2700" t="n">
+        <v>47.9000015258789</v>
+      </c>
+      <c r="F2700" t="n">
+        <v>45.3300018310547</v>
+      </c>
+      <c r="G2700" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2701">
+      <c r="A2701" s="1" t="n">
         <v>46253.2916666667</v>
       </c>
-      <c r="B2700" t="n">
+      <c r="B2701" t="n">
         <v>6165794</v>
       </c>
-      <c r="C2700" t="n">
+      <c r="C2701" t="n">
         <v>45.6100006103516</v>
       </c>
-      <c r="D2700" t="n">
+      <c r="D2701" t="n">
         <v>43.75</v>
       </c>
-      <c r="E2700" t="n">
+      <c r="E2701" t="n">
         <v>45.4099998474121</v>
       </c>
-      <c r="F2700" t="n">
+      <c r="F2701" t="n">
         <v>43.9599990844727</v>
       </c>
-      <c r="G2700" t="s">
+      <c r="G2701" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2702">
+      <c r="A2702" s="1" t="n">
+        <v>46254.2916666667</v>
+      </c>
+      <c r="B2702" t="n">
+        <v>4013724</v>
+      </c>
+      <c r="C2702" t="n">
+        <v>44.1049995422363</v>
+      </c>
+      <c r="D2702" t="n">
+        <v>42.6049995422363</v>
+      </c>
+      <c r="E2702" t="n">
+        <v>44.0950012207031</v>
+      </c>
+      <c r="F2702" t="n">
+        <v>43.0099983215332</v>
+      </c>
+      <c r="G2702" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -62649,8 +62649,31 @@
       <c r="E2708" t="n">
         <v>43.4799995422363</v>
       </c>
-      <c r="F2708"/>
+      <c r="F2708" t="n">
+        <v>43.5750007629395</v>
+      </c>
       <c r="G2708" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2709">
+      <c r="A2709" s="1" t="n">
+        <v>46262.2916666667</v>
+      </c>
+      <c r="B2709" t="n">
+        <v>2879706</v>
+      </c>
+      <c r="C2709" t="n">
+        <v>44.189998626709</v>
+      </c>
+      <c r="D2709" t="n">
+        <v>43.1549987792969</v>
+      </c>
+      <c r="E2709" t="n">
+        <v>43.9900016784668</v>
+      </c>
+      <c r="F2709"/>
+      <c r="G2709" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -62672,8 +62672,31 @@
       <c r="E2709" t="n">
         <v>43.9900016784668</v>
       </c>
-      <c r="F2709"/>
+      <c r="F2709" t="n">
+        <v>43.3400001525879</v>
+      </c>
       <c r="G2709" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2710">
+      <c r="A2710" s="1" t="n">
+        <v>46265.2916666667</v>
+      </c>
+      <c r="B2710" t="n">
+        <v>2728256</v>
+      </c>
+      <c r="C2710" t="n">
+        <v>43.9300003051758</v>
+      </c>
+      <c r="D2710" t="n">
+        <v>42.9599990844727</v>
+      </c>
+      <c r="E2710" t="n">
+        <v>43.0999984741211</v>
+      </c>
+      <c r="F2710"/>
+      <c r="G2710" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -62817,6 +62817,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2716">
+      <c r="A2716" s="1" t="n">
+        <v>46274.2916666667</v>
+      </c>
+      <c r="B2716" t="n">
+        <v>2760682</v>
+      </c>
+      <c r="C2716" t="n">
+        <v>45.2849998474121</v>
+      </c>
+      <c r="D2716" t="n">
+        <v>43.7150001525879</v>
+      </c>
+      <c r="E2716" t="n">
+        <v>45.185001373291</v>
+      </c>
+      <c r="F2716" t="n">
+        <v>44.5200004577637</v>
+      </c>
+      <c r="G2716" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2717">
+      <c r="A2717" s="1" t="n">
+        <v>46275.2916666667</v>
+      </c>
+      <c r="B2717" t="n">
+        <v>3093760</v>
+      </c>
+      <c r="C2717" t="n">
+        <v>45.0299987792969</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>43.0950012207031</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>44.7200012207031</v>
+      </c>
+      <c r="F2717" t="n">
+        <v>43.6300010681152</v>
+      </c>
+      <c r="G2717" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/STMMI.MI.xlsx
+++ b/data/STMMI.MI.xlsx
@@ -62863,6 +62863,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2718">
+      <c r="A2718" s="1" t="n">
+        <v>46276.2916666667</v>
+      </c>
+      <c r="B2718" t="n">
+        <v>3001305</v>
+      </c>
+      <c r="C2718" t="n">
+        <v>44.6949996948242</v>
+      </c>
+      <c r="D2718" t="n">
+        <v>43.5099983215332</v>
+      </c>
+      <c r="E2718" t="n">
+        <v>43.7400016784668</v>
+      </c>
+      <c r="F2718" t="n">
+        <v>44.6699981689453</v>
+      </c>
+      <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
